--- a/49896_Cuenca_Chamaya/_raw_reportes_xlsx/IDConfig_64909_completo.xlsx
+++ b/49896_Cuenca_Chamaya/_raw_reportes_xlsx/IDConfig_64909_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R682a8c6f7e6d4507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4e793eaac1e241e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.9549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2669</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.7533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49896_Cuenca_Chamaya/_raw_reportes_xlsx/IDConfig_64909_completo.xlsx
+++ b/49896_Cuenca_Chamaya/_raw_reportes_xlsx/IDConfig_64909_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4e793eaac1e241e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3256c9542ea741d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,81 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.9002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.1831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
